--- a/Team-Data/2007-08/2-20-2007-08.xlsx
+++ b/Team-Data/2007-08/2-20-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
         <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.423</v>
+        <v>0.431</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -679,37 +746,37 @@
         <v>35</v>
       </c>
       <c r="J2" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.329</v>
+        <v>0.324</v>
       </c>
       <c r="O2" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P2" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R2" t="n">
         <v>12.5</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T2" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U2" t="n">
         <v>21.1</v>
@@ -718,7 +785,7 @@
         <v>15.2</v>
       </c>
       <c r="W2" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X2" t="n">
         <v>5.8</v>
@@ -727,19 +794,19 @@
         <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA2" t="n">
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -748,16 +815,16 @@
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>22</v>
@@ -772,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -787,16 +854,16 @@
         <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
         <v>20</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>0.788</v>
+        <v>0.804</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J3" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="O3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="P3" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U3" t="n">
         <v>21.8</v>
@@ -909,19 +976,19 @@
         <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,19 +1018,19 @@
         <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -981,19 +1048,19 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
         <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
         <v>5</v>
@@ -1151,7 +1218,7 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>16</v>
@@ -1169,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
         <v>35.6</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
         <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0.745</v>
       </c>
       <c r="R5" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
         <v>21.2</v>
@@ -1264,7 +1331,7 @@
         <v>14.7</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5</v>
@@ -1273,31 +1340,31 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
@@ -1309,7 +1376,7 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
@@ -1318,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1333,31 +1400,31 @@
         <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
         <v>13</v>
       </c>
-      <c r="AW5" t="n">
-        <v>12</v>
-      </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1389,37 +1456,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="H6" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
         <v>82.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
         <v>18.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O6" t="n">
         <v>18.2</v>
@@ -1428,7 +1495,7 @@
         <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R6" t="n">
         <v>13</v>
@@ -1449,25 +1516,25 @@
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y6" t="n">
         <v>4.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA6" t="n">
         <v>19.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>9</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1500,7 +1567,7 @@
         <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>26</v>
@@ -1530,16 +1597,16 @@
         <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>0.648</v>
+        <v>0.66</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.462</v>
@@ -1601,40 +1668,40 @@
         <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.9</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T7" t="n">
         <v>42.5</v>
       </c>
       <c r="U7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V7" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>21.8</v>
@@ -1643,13 +1710,13 @@
         <v>21.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>6</v>
@@ -1664,28 +1731,28 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1697,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
@@ -1706,10 +1773,10 @@
         <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1721,10 +1788,10 @@
         <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1852,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>10</v>
@@ -1882,10 +1949,10 @@
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>0.722</v>
+        <v>0.736</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,28 +2020,28 @@
         <v>36.4</v>
       </c>
       <c r="J9" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.758</v>
+        <v>0.755</v>
       </c>
       <c r="R9" t="n">
         <v>11.6</v>
@@ -1989,7 +2056,7 @@
         <v>22.6</v>
       </c>
       <c r="V9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
@@ -2001,7 +2068,7 @@
         <v>3.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
         <v>20.3</v>
@@ -2010,10 +2077,10 @@
         <v>97.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,13 +2095,13 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2079,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -2117,64 +2184,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
         <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J10" t="n">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.458</v>
       </c>
       <c r="L10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O10" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
         <v>12.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U10" t="n">
         <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
         <v>4.4</v>
@@ -2183,28 +2250,28 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.1</v>
+        <v>109.9</v>
       </c>
       <c r="AC10" t="n">
         <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2228,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2240,10 +2307,10 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2255,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>17</v>
@@ -2401,16 +2468,16 @@
         <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN11" t="n">
         <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2443,10 +2510,10 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>0.389</v>
+        <v>0.396</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,7 +2566,7 @@
         <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2520,46 +2587,46 @@
         <v>24.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R12" t="n">
         <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V12" t="n">
         <v>15.9</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="AA12" t="n">
         <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.4</v>
+        <v>102.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2574,7 +2641,7 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
         <v>2</v>
@@ -2598,16 +2665,16 @@
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
@@ -2616,10 +2683,10 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.353</v>
+        <v>0.34</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,46 +2748,46 @@
         <v>34.6</v>
       </c>
       <c r="J13" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
         <v>12.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="O13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P13" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0.79</v>
       </c>
       <c r="R13" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>14.5</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>5.1</v>
@@ -2729,16 +2796,16 @@
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.3</v>
+        <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
         <v>30</v>
@@ -2747,10 +2814,10 @@
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH13" t="n">
         <v>20</v>
@@ -2765,13 +2832,13 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
         <v>27</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>9</v>
@@ -2786,28 +2853,28 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M14" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O14" t="n">
         <v>21.6</v>
@@ -2884,28 +2951,28 @@
         <v>28.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
@@ -2917,22 +2984,22 @@
         <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.8</v>
+        <v>107.4</v>
       </c>
       <c r="AC14" t="n">
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2941,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2950,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>10</v>
@@ -2959,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
@@ -2971,22 +3038,22 @@
         <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>0.259</v>
+        <v>0.264</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L15" t="n">
         <v>7.9</v>
@@ -3057,13 +3124,13 @@
         <v>21.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q15" t="n">
         <v>0.737</v>
@@ -3072,13 +3139,13 @@
         <v>10.1</v>
       </c>
       <c r="S15" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
         <v>41.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V15" t="n">
         <v>16</v>
@@ -3087,25 +3154,25 @@
         <v>5.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>19.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.1</v>
+        <v>-4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
@@ -3126,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3150,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>18</v>
@@ -3159,10 +3226,10 @@
         <v>24</v>
       </c>
       <c r="AV15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW15" t="n">
         <v>28</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>29</v>
       </c>
       <c r="AX15" t="n">
         <v>7</v>
@@ -3177,10 +3244,10 @@
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3344,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
@@ -3353,10 +3420,10 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
         <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.37</v>
+        <v>0.358</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3421,16 +3488,16 @@
         <v>16.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P17" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R17" t="n">
         <v>11.9</v>
@@ -3439,7 +3506,7 @@
         <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U17" t="n">
         <v>21.3</v>
@@ -3454,22 +3521,22 @@
         <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z17" t="n">
         <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
@@ -3481,7 +3548,7 @@
         <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3496,13 +3563,13 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
         <v>26</v>
@@ -3517,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU17" t="n">
         <v>17</v>
@@ -3535,13 +3602,13 @@
         <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,19 +3733,19 @@
         <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
         <v>28</v>
@@ -3690,13 +3757,13 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
         <v>12</v>
@@ -3708,7 +3775,7 @@
         <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.444</v>
+        <v>0.434</v>
       </c>
       <c r="H19" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="J19" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="R19" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T19" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U19" t="n">
         <v>23.9</v>
@@ -3824,28 +3891,28 @@
         <v>22.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,10 +3927,10 @@
         <v>21</v>
       </c>
       <c r="AM19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3872,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3881,13 +3948,13 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -3937,46 +4004,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0.712</v>
+        <v>0.706</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.461</v>
       </c>
       <c r="L20" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>20.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
@@ -3991,37 +4058,37 @@
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF20" t="n">
         <v>3</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
@@ -4039,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>7</v>
@@ -4060,7 +4127,7 @@
         <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>25</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
         <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.296</v>
+        <v>0.302</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,46 +4204,46 @@
         <v>35</v>
       </c>
       <c r="J21" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.332</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P21" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0.725</v>
       </c>
       <c r="R21" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V21" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W21" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
@@ -4188,16 +4255,16 @@
         <v>21.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.2</v>
+        <v>-5.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,13 +4276,13 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
@@ -4224,19 +4291,19 @@
         <v>19</v>
       </c>
       <c r="AM21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
         <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
         <v>7</v>
@@ -4251,25 +4318,25 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
         <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.607</v>
+        <v>0.618</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>36.8</v>
       </c>
       <c r="J22" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.469</v>
@@ -4331,37 +4398,37 @@
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O22" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W22" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y22" t="n">
         <v>4.3</v>
@@ -4373,10 +4440,10 @@
         <v>23.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4385,10 +4452,10 @@
         <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4397,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4409,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4421,10 +4488,10 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
@@ -4439,7 +4506,7 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4513,16 +4580,16 @@
         <v>11.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.317</v>
+        <v>0.313</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
         <v>25.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.702</v>
+        <v>0.701</v>
       </c>
       <c r="R23" t="n">
         <v>13</v>
@@ -4534,31 +4601,31 @@
         <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.8</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
@@ -4570,19 +4637,19 @@
         <v>20</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4597,7 +4664,7 @@
         <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,16 +4676,16 @@
         <v>29</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4633,10 +4700,10 @@
         <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -4665,67 +4732,67 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E24" t="n">
         <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.494</v>
+        <v>0.493</v>
       </c>
       <c r="L24" t="n">
         <v>8.9</v>
       </c>
       <c r="M24" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P24" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R24" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="n">
         <v>32.2</v>
       </c>
       <c r="T24" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U24" t="n">
         <v>27.2</v>
       </c>
       <c r="V24" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W24" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="n">
         <v>3.7</v>
@@ -4734,16 +4801,16 @@
         <v>19.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.1</v>
+        <v>109.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4800,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>-0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4949,7 +5016,7 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>18</v>
@@ -4964,7 +5031,7 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4973,7 +5040,7 @@
         <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
@@ -5000,7 +5067,7 @@
         <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
@@ -5047,43 +5114,43 @@
         <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
         <v>17.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P26" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0.792</v>
       </c>
       <c r="R26" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S26" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T26" t="n">
         <v>40.1</v>
       </c>
       <c r="U26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V26" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W26" t="n">
         <v>8.1</v>
@@ -5092,58 +5159,58 @@
         <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA26" t="n">
         <v>23</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.6</v>
+        <v>100.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
         <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -5155,7 +5222,7 @@
         <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5170,7 +5237,7 @@
         <v>28</v>
       </c>
       <c r="AY26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ26" t="n">
         <v>23</v>
@@ -5179,7 +5246,7 @@
         <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>5.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>6</v>
       </c>
       <c r="AF27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG27" t="n">
         <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,7 +5377,7 @@
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5319,10 +5386,10 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
@@ -5340,7 +5407,7 @@
         <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV27" t="n">
         <v>5</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>-7</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
         <v>27</v>
@@ -5495,7 +5562,7 @@
         <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM28" t="n">
         <v>26</v>
@@ -5537,13 +5604,13 @@
         <v>23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
         <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>28</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -5575,85 +5642,85 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>23</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J29" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L29" t="n">
         <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.424</v>
+        <v>0.421</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P29" t="n">
         <v>20.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.6</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA29" t="n">
         <v>18</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,16 +5732,16 @@
         <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP29" t="n">
         <v>29</v>
@@ -5701,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5710,25 +5777,25 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY29" t="n">
         <v>6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -5835,25 +5902,25 @@
         <v>6.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>6</v>
       </c>
       <c r="AF30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5871,7 +5938,7 @@
         <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
@@ -5880,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
         <v>22</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,10 +6099,10 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>21</v>
@@ -6047,10 +6114,10 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6065,7 +6132,7 @@
         <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6074,16 +6141,16 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6092,7 +6159,7 @@
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-20-2007-08</t>
+          <t>2008-02-20</t>
         </is>
       </c>
     </row>
